--- a/data/trans_orig/P2A_enfcro_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2007</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97891</t>
+          <t>98048</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129902</t>
+          <t>130844</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113091</t>
+          <t>113793</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>146452</t>
+          <t>147027</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>221538</t>
+          <t>219135</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>269480</t>
+          <t>266011</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>49,83%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>143108</t>
+          <t>142166</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>175119</t>
+          <t>174962</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114386</t>
+          <t>113811</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147747</t>
+          <t>147045</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>264368</t>
+          <t>267837</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>312310</t>
+          <t>314713</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,95%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>175421</t>
+          <t>178836</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>220091</t>
+          <t>223183</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>281009</t>
+          <t>281513</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>323773</t>
+          <t>327518</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>471239</t>
+          <t>468420</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>533153</t>
+          <t>533059</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>272984</t>
+          <t>269892</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>317654</t>
+          <t>314239</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>180176</t>
+          <t>176431</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>222940</t>
+          <t>222436</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>463871</t>
+          <t>463965</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>525785</t>
+          <t>528604</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>53,02%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122454</t>
+          <t>122627</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156988</t>
+          <t>157876</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>208071</t>
+          <t>209430</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>243022</t>
+          <t>244323</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>339695</t>
+          <t>337171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>390733</t>
+          <t>391111</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,78%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>161858</t>
+          <t>160970</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>196392</t>
+          <t>196219</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92390</t>
+          <t>91089</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127341</t>
+          <t>125982</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>263525</t>
+          <t>263147</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>314563</t>
+          <t>317087</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,47%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>162902</t>
+          <t>161889</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>201761</t>
+          <t>198512</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>238612</t>
+          <t>236573</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>273807</t>
+          <t>272937</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>411623</t>
+          <t>410392</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>463053</t>
+          <t>462405</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,33%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156910</t>
+          <t>160159</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>195769</t>
+          <t>196782</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,58%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97649</t>
+          <t>98519</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132844</t>
+          <t>134883</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>267074</t>
+          <t>267722</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>318504</t>
+          <t>319735</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,79%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75441</t>
+          <t>74721</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103660</t>
+          <t>102903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>104256</t>
+          <t>105247</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133115</t>
+          <t>133896</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>187282</t>
+          <t>185234</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>229025</t>
+          <t>225779</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>54,94%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99648</t>
+          <t>100405</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>127867</t>
+          <t>128587</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74553</t>
+          <t>73772</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>103412</t>
+          <t>102421</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>181951</t>
+          <t>185197</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>223694</t>
+          <t>225742</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,93%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>119235</t>
+          <t>119347</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>152051</t>
+          <t>152603</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>160263</t>
+          <t>160625</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>193119</t>
+          <t>193255</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>291475</t>
+          <t>290538</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>336627</t>
+          <t>336385</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,28%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>118760</t>
+          <t>118208</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151576</t>
+          <t>151464</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>85025</t>
+          <t>84889</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>117881</t>
+          <t>117519</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>212328</t>
+          <t>212570</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>257480</t>
+          <t>258417</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,07%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>228637</t>
+          <t>227023</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>277505</t>
+          <t>275491</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>348034</t>
+          <t>346889</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>396846</t>
+          <t>396031</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>588644</t>
+          <t>590911</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>662222</t>
+          <t>662330</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>337522</t>
+          <t>339536</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>386390</t>
+          <t>388004</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>241373</t>
+          <t>242188</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>290185</t>
+          <t>291330</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>591024</t>
+          <t>590916</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>664602</t>
+          <t>662335</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>318452</t>
+          <t>315060</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>373809</t>
+          <t>369892</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>432516</t>
+          <t>432443</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>486788</t>
+          <t>486517</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>761193</t>
+          <t>763445</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>842618</t>
+          <t>840115</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,01%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>369986</t>
+          <t>373903</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>425343</t>
+          <t>428735</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>296723</t>
+          <t>296994</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>350995</t>
+          <t>351068</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>684688</t>
+          <t>687191</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>766113</t>
+          <t>763861</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>50,01%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1395018</t>
+          <t>1395138</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1518207</t>
+          <t>1511228</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1984896</t>
+          <t>1987034</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2100982</t>
+          <t>2098254</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3412677</t>
+          <t>3411780</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3580049</t>
+          <t>3578155</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,76%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1758336</t>
+          <t>1765315</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1881525</t>
+          <t>1881405</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1278215</t>
+          <t>1280943</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1394301</t>
+          <t>1392163</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3075692</t>
+          <t>3077586</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3243064</t>
+          <t>3243961</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2012</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>159136</t>
+          <t>160936</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>193869</t>
+          <t>193343</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>204358</t>
+          <t>205094</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>234224</t>
+          <t>235582</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>372712</t>
+          <t>370927</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>419738</t>
+          <t>418244</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,87%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>100869</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>135602</t>
+          <t>133802</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53021</t>
+          <t>51663</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82887</t>
+          <t>82151</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>162245</t>
+          <t>163739</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>209271</t>
+          <t>211056</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>234562</t>
+          <t>234589</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>281011</t>
+          <t>281180</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>333722</t>
+          <t>335842</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>379976</t>
+          <t>378506</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>581933</t>
+          <t>580403</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>649922</t>
+          <t>644108</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>62,58%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>224516</t>
+          <t>224347</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>270965</t>
+          <t>270938</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>143789</t>
+          <t>145259</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>190043</t>
+          <t>187923</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>379370</t>
+          <t>385184</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>447359</t>
+          <t>448889</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,61%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>170177</t>
+          <t>172589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>206939</t>
+          <t>208073</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>210736</t>
+          <t>211368</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>246257</t>
+          <t>248456</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>396067</t>
+          <t>395711</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>446609</t>
+          <t>444298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>66,81%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117107</t>
+          <t>115973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>153869</t>
+          <t>151457</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94763</t>
+          <t>92564</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>130284</t>
+          <t>129652</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>218457</t>
+          <t>220768</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>268999</t>
+          <t>269355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,5%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>191847</t>
+          <t>193709</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>233370</t>
+          <t>231754</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>254013</t>
+          <t>253520</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>289851</t>
+          <t>291486</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>456220</t>
+          <t>458551</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>509140</t>
+          <t>510595</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,93%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>140612</t>
+          <t>142228</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>182135</t>
+          <t>180273</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>99100</t>
+          <t>97465</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134938</t>
+          <t>135431</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>253793</t>
+          <t>252338</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>306713</t>
+          <t>304382</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,9%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99494</t>
+          <t>97426</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129092</t>
+          <t>128385</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163068</t>
+          <t>162059</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>185959</t>
+          <t>186048</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>269995</t>
+          <t>268176</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>308914</t>
+          <t>308902</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83526</t>
+          <t>84233</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>113124</t>
+          <t>115192</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33632</t>
+          <t>33543</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56523</t>
+          <t>57532</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>123295</t>
+          <t>123307</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>162214</t>
+          <t>164033</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>154564</t>
+          <t>153701</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>188653</t>
+          <t>186613</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>201188</t>
+          <t>201207</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>228922</t>
+          <t>229515</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>365467</t>
+          <t>366084</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>408690</t>
+          <t>409050</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,83%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85328</t>
+          <t>87368</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>119417</t>
+          <t>120280</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51109</t>
+          <t>50516</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>78843</t>
+          <t>78824</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>145322</t>
+          <t>144962</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>188545</t>
+          <t>187928</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>352959</t>
+          <t>350010</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>408180</t>
+          <t>406386</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>440731</t>
+          <t>442226</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>495517</t>
+          <t>492434</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>812943</t>
+          <t>815230</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>886765</t>
+          <t>885339</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,26%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>254608</t>
+          <t>256402</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>309829</t>
+          <t>312778</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>198336</t>
+          <t>201419</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>253122</t>
+          <t>251627</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>469876</t>
+          <t>471302</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>543698</t>
+          <t>541411</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>313085</t>
+          <t>313803</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>372924</t>
+          <t>369708</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>436553</t>
+          <t>434555</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>494105</t>
+          <t>494178</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>767422</t>
+          <t>764404</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>847853</t>
+          <t>847344</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,88%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,86%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>406174</t>
+          <t>409390</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>466013</t>
+          <t>465295</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>329748</t>
+          <t>329675</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>387300</t>
+          <t>389298</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>755098</t>
+          <t>755607</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>835529</t>
+          <t>838547</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>52,31%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1789667</t>
+          <t>1787734</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1908688</t>
+          <t>1905940</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2346785</t>
+          <t>2344188</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2463521</t>
+          <t>2461200</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4170243</t>
+          <t>4171772</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4338258</t>
+          <t>4338291</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1518091</t>
+          <t>1520839</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1637112</t>
+          <t>1639045</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1094788</t>
+          <t>1097109</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1211524</t>
+          <t>1214121</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2646830</t>
+          <t>2646797</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2814845</t>
+          <t>2813316</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2016</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>139471</t>
+          <t>137414</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>174308</t>
+          <t>174294</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>170673</t>
+          <t>171528</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>202937</t>
+          <t>202710</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>318387</t>
+          <t>315717</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>368408</t>
+          <t>366845</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>62,98%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119453</t>
+          <t>119467</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154290</t>
+          <t>156347</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85766</t>
+          <t>85993</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>118030</t>
+          <t>117175</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>214056</t>
+          <t>215619</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>264077</t>
+          <t>266747</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,8%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>257737</t>
+          <t>256881</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>304487</t>
+          <t>303372</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>343945</t>
+          <t>343848</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>387447</t>
+          <t>386303</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>615659</t>
+          <t>613839</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>678078</t>
+          <t>677523</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,06%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>198088</t>
+          <t>199203</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>244838</t>
+          <t>245694</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135637</t>
+          <t>136781</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>179139</t>
+          <t>179236</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>347581</t>
+          <t>348136</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>410000</t>
+          <t>411820</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>147211</t>
+          <t>146114</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>179554</t>
+          <t>181318</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>183767</t>
+          <t>187161</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>219750</t>
+          <t>221300</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>343050</t>
+          <t>342279</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>392438</t>
+          <t>389894</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,54%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>139011</t>
+          <t>137247</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>171354</t>
+          <t>172451</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116559</t>
+          <t>115009</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>152542</t>
+          <t>149148</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>262436</t>
+          <t>264980</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>311824</t>
+          <t>312595</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>186970</t>
+          <t>185700</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>225539</t>
+          <t>224793</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>251307</t>
+          <t>250877</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>289436</t>
+          <t>287028</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>446713</t>
+          <t>448734</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>503714</t>
+          <t>503208</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,45%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>144425</t>
+          <t>145171</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>182994</t>
+          <t>184264</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97847</t>
+          <t>100255</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>135976</t>
+          <t>136406</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>253533</t>
+          <t>254039</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>310534</t>
+          <t>308513</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,74%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92956</t>
+          <t>92406</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>122729</t>
+          <t>120901</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>118319</t>
+          <t>117534</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>145573</t>
+          <t>146242</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>220743</t>
+          <t>220741</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>261206</t>
+          <t>262073</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,97%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>88492</t>
+          <t>90320</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>118265</t>
+          <t>118815</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73014</t>
+          <t>72345</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>100268</t>
+          <t>101053</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>168602</t>
+          <t>167735</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>209065</t>
+          <t>209067</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>101557</t>
+          <t>101498</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>134735</t>
+          <t>133911</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>137413</t>
+          <t>139174</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>170916</t>
+          <t>173037</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>249794</t>
+          <t>246733</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>297837</t>
+          <t>294053</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>54,84%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>128388</t>
+          <t>129212</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>161566</t>
+          <t>161625</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>102199</t>
+          <t>100078</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>135702</t>
+          <t>133941</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>238401</t>
+          <t>242185</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>286444</t>
+          <t>289505</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,99%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>252682</t>
+          <t>245989</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>307767</t>
+          <t>301781</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>346099</t>
+          <t>347160</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>400708</t>
+          <t>401747</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>613673</t>
+          <t>617052</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>693058</t>
+          <t>692195</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,42%</t>
+          <t>51,36%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>348791</t>
+          <t>354777</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>403876</t>
+          <t>410569</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>290586</t>
+          <t>289547</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>345195</t>
+          <t>344134</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>654794</t>
+          <t>655657</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>734179</t>
+          <t>730800</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,22%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>348685</t>
+          <t>345437</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>404140</t>
+          <t>403384</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>456241</t>
+          <t>456222</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>512974</t>
+          <t>515466</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>823145</t>
+          <t>817486</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>905048</t>
+          <t>899358</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>374443</t>
+          <t>375199</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>429898</t>
+          <t>433146</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>313193</t>
+          <t>310701</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>369926</t>
+          <t>369945</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>699702</t>
+          <t>705392</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>781605</t>
+          <t>787264</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,06%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1628133</t>
+          <t>1629433</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1749665</t>
+          <t>1743343</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2113439</t>
+          <t>2119804</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2230684</t>
+          <t>2232713</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3773554</t>
+          <t>3775991</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3942718</t>
+          <t>3938798</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,76%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1644685</t>
+          <t>1651007</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1766217</t>
+          <t>1764917</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1313858</t>
+          <t>1311829</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1431103</t>
+          <t>1424738</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2996174</t>
+          <t>3000094</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3165338</t>
+          <t>3162901</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,58%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2023</t>
+          <t>Hogares según si tienen personas con enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>164354</t>
+          <t>164792</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>205076</t>
+          <t>206038</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>182743</t>
+          <t>183279</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>209199</t>
+          <t>210217</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>358868</t>
+          <t>358802</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>408184</t>
+          <t>406616</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>67,65%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>106367</t>
+          <t>105405</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>147089</t>
+          <t>146651</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80436</t>
+          <t>79418</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106892</t>
+          <t>106356</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>192893</t>
+          <t>194461</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>242209</t>
+          <t>242275</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,31%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>143613</t>
+          <t>143685</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>197718</t>
+          <t>197447</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>178220</t>
+          <t>174942</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>216602</t>
+          <t>214312</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>331320</t>
+          <t>332070</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>398531</t>
+          <t>402171</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>320672</t>
+          <t>320943</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>374777</t>
+          <t>374705</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>298367</t>
+          <t>300657</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336749</t>
+          <t>340027</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>634828</t>
+          <t>631188</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>702039</t>
+          <t>701289</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,87%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>109918</t>
+          <t>112697</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>146020</t>
+          <t>145188</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>141657</t>
+          <t>142142</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>174152</t>
+          <t>172811</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,88%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>264774</t>
+          <t>259929</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>309481</t>
+          <t>309209</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,49%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>170030</t>
+          <t>170862</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>206132</t>
+          <t>203353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>174976</t>
+          <t>176317</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>207471</t>
+          <t>206986</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>355697</t>
+          <t>355969</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>400404</t>
+          <t>405249</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,92%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107130</t>
+          <t>106942</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>150249</t>
+          <t>147254</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110863</t>
+          <t>110053</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>232528</t>
+          <t>233090</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>230917</t>
+          <t>222189</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>361996</t>
+          <t>361616</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>45,87%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>162308</t>
+          <t>165303</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>205427</t>
+          <t>205615</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>243190</t>
+          <t>242628</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364855</t>
+          <t>365665</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>426278</t>
+          <t>426658</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>557357</t>
+          <t>566085</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>71,81%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12381</t>
+          <t>12293</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25656</t>
+          <t>25415</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13441</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33888</t>
+          <t>33098</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29383</t>
+          <t>29880</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54364</t>
+          <t>53504</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153086</t>
+          <t>153327</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166361</t>
+          <t>166449</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>224891</t>
+          <t>225681</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>245338</t>
+          <t>245693</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>383157</t>
+          <t>384017</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>408138</t>
+          <t>407641</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>119052</t>
+          <t>117824</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>149022</t>
+          <t>148052</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>117580</t>
+          <t>119026</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>143843</t>
+          <t>143983</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>244825</t>
+          <t>246785</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>283332</t>
+          <t>282182</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,58%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>120614</t>
+          <t>121584</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>150584</t>
+          <t>151812</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>113213</t>
+          <t>113073</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>139476</t>
+          <t>138030</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>243360</t>
+          <t>244510</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>281867</t>
+          <t>279907</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,14%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>114802</t>
+          <t>117006</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>163293</t>
+          <t>164795</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>218874</t>
+          <t>219390</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>584021</t>
+          <t>616480</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>350593</t>
+          <t>349389</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>887919</t>
+          <t>854127</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,26%</t>
+          <t>57,96%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>460986</t>
+          <t>459484</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>509477</t>
+          <t>507273</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>265244</t>
+          <t>232785</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>630391</t>
+          <t>629875</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>585625</t>
+          <t>619417</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1122951</t>
+          <t>1124155</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>90207</t>
+          <t>87766</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>286428</t>
+          <t>287957</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>276022</t>
+          <t>274894</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>319476</t>
+          <t>318720</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>308869</t>
+          <t>302808</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>601739</t>
+          <t>599254</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>642292</t>
+          <t>640763</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>838513</t>
+          <t>840954</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>398255</t>
+          <t>399011</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>441709</t>
+          <t>442837</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1044713</t>
+          <t>1047198</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1337583</t>
+          <t>1343644</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,61%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>878030</t>
+          <t>851461</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1217031</t>
+          <t>1212100</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1417449</t>
+          <t>1412102</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1988813</t>
+          <t>1968520</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2415351</t>
+          <t>2428411</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3070970</t>
+          <t>3056824</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2242786</t>
+          <t>2247717</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2581787</t>
+          <t>2608356</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1723467</t>
+          <t>1743760</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2294831</t>
+          <t>2300178</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4101127</t>
+          <t>4115273</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4756746</t>
+          <t>4743686</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,14%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_enfcro_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98048</t>
+          <t>99013</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>130844</t>
+          <t>131168</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113793</t>
+          <t>113554</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>147027</t>
+          <t>146234</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>219135</t>
+          <t>220676</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>266011</t>
+          <t>266582</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,94%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>142166</t>
+          <t>141842</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>174962</t>
+          <t>173997</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,09%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113811</t>
+          <t>114604</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147045</t>
+          <t>147284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>267837</t>
+          <t>267266</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>314713</t>
+          <t>313172</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,66%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>178836</t>
+          <t>177599</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>223183</t>
+          <t>221323</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>281513</t>
+          <t>278982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>327518</t>
+          <t>324103</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>468420</t>
+          <t>470117</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>533059</t>
+          <t>534657</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,63%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>269892</t>
+          <t>271752</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>314239</t>
+          <t>315476</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>176431</t>
+          <t>179846</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>222436</t>
+          <t>224967</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>463965</t>
+          <t>462367</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>528604</t>
+          <t>526907</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>122627</t>
+          <t>120010</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>157876</t>
+          <t>157221</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>209430</t>
+          <t>208748</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>244323</t>
+          <t>243502</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>337171</t>
+          <t>339376</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>391111</t>
+          <t>389623</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,55%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160970</t>
+          <t>161625</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>196219</t>
+          <t>198836</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>91089</t>
+          <t>91910</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125982</t>
+          <t>126664</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>263147</t>
+          <t>264635</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>317087</t>
+          <t>314882</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,13%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>161889</t>
+          <t>162020</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>198512</t>
+          <t>198916</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>236573</t>
+          <t>237971</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>272937</t>
+          <t>271646</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>410392</t>
+          <t>410455</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>462405</t>
+          <t>462689</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>63,37%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>160159</t>
+          <t>159755</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>196782</t>
+          <t>196651</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98519</t>
+          <t>99810</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>134883</t>
+          <t>133485</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>267722</t>
+          <t>267438</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>319735</t>
+          <t>319672</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,78%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74721</t>
+          <t>75346</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>102903</t>
+          <t>104013</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105247</t>
+          <t>105012</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133896</t>
+          <t>133429</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>185234</t>
+          <t>185280</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>225779</t>
+          <t>227784</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,43%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100405</t>
+          <t>99295</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128587</t>
+          <t>127962</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>73772</t>
+          <t>74239</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>102421</t>
+          <t>102656</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>185197</t>
+          <t>183192</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>225742</t>
+          <t>225696</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>54,92%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>119347</t>
+          <t>119473</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>152603</t>
+          <t>151274</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>160625</t>
+          <t>160624</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>193255</t>
+          <t>192178</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>69,48%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>290538</t>
+          <t>289610</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>336385</t>
+          <t>336311</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,26%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>118208</t>
+          <t>119537</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151464</t>
+          <t>151338</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>84889</t>
+          <t>85966</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>117519</t>
+          <t>117520</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>212570</t>
+          <t>212644</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>258417</t>
+          <t>259345</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,24%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>227023</t>
+          <t>225560</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>275491</t>
+          <t>276041</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>346889</t>
+          <t>347188</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>396031</t>
+          <t>397362</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>590911</t>
+          <t>589944</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>662330</t>
+          <t>660778</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>339536</t>
+          <t>338986</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>388004</t>
+          <t>389467</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>242188</t>
+          <t>240857</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>291330</t>
+          <t>291031</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>590916</t>
+          <t>592468</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>662335</t>
+          <t>663302</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,93%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>315060</t>
+          <t>315255</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>369892</t>
+          <t>371787</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>432443</t>
+          <t>427647</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>486517</t>
+          <t>484233</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>763445</t>
+          <t>758697</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>840115</t>
+          <t>838291</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,01%</t>
+          <t>54,89%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>373903</t>
+          <t>372008</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>428735</t>
+          <t>428540</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>296994</t>
+          <t>299278</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>351068</t>
+          <t>355864</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>687191</t>
+          <t>689015</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>763861</t>
+          <t>768609</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>50,32%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1395138</t>
+          <t>1400719</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1511228</t>
+          <t>1511926</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>46,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1987034</t>
+          <t>1983020</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2098254</t>
+          <t>2093417</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3411780</t>
+          <t>3414949</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3578155</t>
+          <t>3578136</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1765315</t>
+          <t>1764617</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1881405</t>
+          <t>1875824</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1280943</t>
+          <t>1285780</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1392163</t>
+          <t>1396177</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3077586</t>
+          <t>3077605</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3243961</t>
+          <t>3240792</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,69%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>160936</t>
+          <t>159471</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>193343</t>
+          <t>193501</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>65,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>205094</t>
+          <t>206266</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>235582</t>
+          <t>235848</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>370927</t>
+          <t>374488</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>418244</t>
+          <t>419374</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>72,06%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101395</t>
+          <t>101237</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133802</t>
+          <t>135267</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51663</t>
+          <t>51397</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82151</t>
+          <t>80979</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>163739</t>
+          <t>162609</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>211056</t>
+          <t>207495</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>234589</t>
+          <t>236412</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>281180</t>
+          <t>280322</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>335842</t>
+          <t>335706</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>378506</t>
+          <t>378678</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>580403</t>
+          <t>583105</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>644108</t>
+          <t>650586</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>63,21%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>224347</t>
+          <t>225205</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>270938</t>
+          <t>269115</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>145259</t>
+          <t>145087</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>187923</t>
+          <t>188059</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>385184</t>
+          <t>378706</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>448889</t>
+          <t>446187</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>43,35%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>172589</t>
+          <t>173621</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>208073</t>
+          <t>209525</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>211368</t>
+          <t>209636</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>248456</t>
+          <t>245708</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>395711</t>
+          <t>395615</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>444298</t>
+          <t>445688</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>67,01%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115973</t>
+          <t>114521</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>151457</t>
+          <t>150425</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92564</t>
+          <t>95312</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>129652</t>
+          <t>131384</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>220768</t>
+          <t>219378</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>269355</t>
+          <t>269451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,51%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>193709</t>
+          <t>192681</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>231754</t>
+          <t>231561</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>253520</t>
+          <t>253503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>291486</t>
+          <t>289113</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>458551</t>
+          <t>457126</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>510595</t>
+          <t>510640</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142228</t>
+          <t>142421</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>180273</t>
+          <t>181301</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97465</t>
+          <t>99838</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>135431</t>
+          <t>135448</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>252338</t>
+          <t>252293</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>304382</t>
+          <t>305807</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>40,08%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>97426</t>
+          <t>98473</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>128385</t>
+          <t>128525</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>162059</t>
+          <t>161149</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>186048</t>
+          <t>185719</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>268176</t>
+          <t>268175</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>308902</t>
+          <t>308451</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>71,37%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84233</t>
+          <t>84093</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>115192</t>
+          <t>114145</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33543</t>
+          <t>33872</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>57532</t>
+          <t>58442</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>123307</t>
+          <t>123758</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>164033</t>
+          <t>164034</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>153701</t>
+          <t>156361</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>186613</t>
+          <t>190032</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>201207</t>
+          <t>200317</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>229515</t>
+          <t>229314</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>366084</t>
+          <t>362002</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>409050</t>
+          <t>407833</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,61%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87368</t>
+          <t>83949</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>120280</t>
+          <t>117620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50516</t>
+          <t>50717</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>78824</t>
+          <t>79714</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>144962</t>
+          <t>146179</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>187928</t>
+          <t>192010</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,66%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>350010</t>
+          <t>352999</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>406386</t>
+          <t>408167</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>442226</t>
+          <t>444989</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>492434</t>
+          <t>496407</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,73%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>815230</t>
+          <t>812521</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>885339</t>
+          <t>881626</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>64,99%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>256402</t>
+          <t>254621</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>312778</t>
+          <t>309789</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>201419</t>
+          <t>197446</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>251627</t>
+          <t>248864</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>471302</t>
+          <t>475015</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>541411</t>
+          <t>544120</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,11%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>313803</t>
+          <t>310870</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>369708</t>
+          <t>369281</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>434555</t>
+          <t>438325</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>494178</t>
+          <t>496222</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>764404</t>
+          <t>766830</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>847344</t>
+          <t>844892</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>52,71%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>409390</t>
+          <t>409817</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>465295</t>
+          <t>468228</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>329675</t>
+          <t>327631</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>389298</t>
+          <t>385528</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>755607</t>
+          <t>758059</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>838547</t>
+          <t>836121</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,16%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1787734</t>
+          <t>1781529</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1905940</t>
+          <t>1911230</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2344188</t>
+          <t>2343467</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2461200</t>
+          <t>2459148</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4171772</t>
+          <t>4164479</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4338291</t>
+          <t>4334381</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>59,62%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,05%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1520839</t>
+          <t>1515549</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1639045</t>
+          <t>1645250</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1097109</t>
+          <t>1099161</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1214121</t>
+          <t>1214842</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2646797</t>
+          <t>2650707</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2813316</t>
+          <t>2820609</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,38%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>137414</t>
+          <t>135974</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>174294</t>
+          <t>173052</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>171528</t>
+          <t>171944</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>202710</t>
+          <t>204158</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>315717</t>
+          <t>318597</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>366845</t>
+          <t>368022</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,18%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119467</t>
+          <t>120709</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>156347</t>
+          <t>157787</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>85993</t>
+          <t>84545</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>117175</t>
+          <t>116759</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>215619</t>
+          <t>214442</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>266747</t>
+          <t>263867</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,3%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>256881</t>
+          <t>258947</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>303372</t>
+          <t>303705</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>343848</t>
+          <t>343526</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>386303</t>
+          <t>386116</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>613839</t>
+          <t>616437</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>677523</t>
+          <t>679428</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,24%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>199203</t>
+          <t>198870</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>245694</t>
+          <t>243628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>136781</t>
+          <t>136968</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>179236</t>
+          <t>179558</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>348136</t>
+          <t>346231</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>411820</t>
+          <t>409222</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,9%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>146114</t>
+          <t>146343</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>181318</t>
+          <t>180216</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>187161</t>
+          <t>186838</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>221300</t>
+          <t>223169</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>342279</t>
+          <t>341512</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>389894</t>
+          <t>392278</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,9%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>137247</t>
+          <t>138349</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>172451</t>
+          <t>172222</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>115009</t>
+          <t>113140</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149148</t>
+          <t>149471</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264980</t>
+          <t>262596</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>312595</t>
+          <t>313362</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,85%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>185700</t>
+          <t>187017</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>224793</t>
+          <t>225471</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>250877</t>
+          <t>251887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>287028</t>
+          <t>288242</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>448734</t>
+          <t>448929</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>503208</t>
+          <t>503189</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>145171</t>
+          <t>144493</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>184264</t>
+          <t>182947</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>100255</t>
+          <t>99041</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>136406</t>
+          <t>135396</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>254039</t>
+          <t>254058</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>308513</t>
+          <t>308318</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,72%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92406</t>
+          <t>93884</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>120901</t>
+          <t>123626</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>117534</t>
+          <t>117792</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>146242</t>
+          <t>145431</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>220741</t>
+          <t>217500</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>262073</t>
+          <t>258367</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,11%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90320</t>
+          <t>87595</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>118815</t>
+          <t>117337</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72345</t>
+          <t>73156</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101053</t>
+          <t>100795</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>167735</t>
+          <t>171441</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>209067</t>
+          <t>212308</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>49,4%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>101498</t>
+          <t>101261</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>133911</t>
+          <t>133987</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>139174</t>
+          <t>136918</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>173037</t>
+          <t>168805</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>50,96%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>246733</t>
+          <t>248761</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>294053</t>
+          <t>295660</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,01%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>55,14%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>129212</t>
+          <t>129136</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>161625</t>
+          <t>161862</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>100078</t>
+          <t>104310</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>133941</t>
+          <t>136197</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>242185</t>
+          <t>240578</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>289505</t>
+          <t>287477</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>53,61%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>245989</t>
+          <t>252393</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>301781</t>
+          <t>305709</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>347160</t>
+          <t>345465</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>401747</t>
+          <t>399130</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>617052</t>
+          <t>613730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>692195</t>
+          <t>688245</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,06%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>354777</t>
+          <t>350849</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>410569</t>
+          <t>404165</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>289547</t>
+          <t>292164</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>344134</t>
+          <t>345829</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>655657</t>
+          <t>659607</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>730800</t>
+          <t>734122</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,47%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>345437</t>
+          <t>345941</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>403384</t>
+          <t>404914</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>456222</t>
+          <t>455912</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>515466</t>
+          <t>515703</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>817486</t>
+          <t>820305</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>899358</t>
+          <t>897433</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,92%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>375199</t>
+          <t>373669</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>433146</t>
+          <t>432642</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>310701</t>
+          <t>310464</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>369945</t>
+          <t>370255</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>705392</t>
+          <t>707317</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>787264</t>
+          <t>784445</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>48,88%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1629433</t>
+          <t>1624172</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1743343</t>
+          <t>1744035</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2119804</t>
+          <t>2111362</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2232713</t>
+          <t>2229526</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3775991</t>
+          <t>3777097</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3938798</t>
+          <t>3939736</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,78%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1651007</t>
+          <t>1650315</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1764917</t>
+          <t>1770178</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>48,64%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1311829</t>
+          <t>1315016</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1424738</t>
+          <t>1433180</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3000094</t>
+          <t>2999156</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3162901</t>
+          <t>3161795</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>184716</t>
+          <t>177274</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>164792</t>
+          <t>159934</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>206038</t>
+          <t>195254</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>197039</t>
+          <t>203243</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>183279</t>
+          <t>187776</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>210217</t>
+          <t>217004</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>381755</t>
+          <t>380516</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>358802</t>
+          <t>356867</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>406616</t>
+          <t>404847</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>63,76%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>126727</t>
+          <t>141571</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105405</t>
+          <t>123591</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146651</t>
+          <t>158911</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>92596</t>
+          <t>112818</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>79418</t>
+          <t>99057</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>106356</t>
+          <t>128285</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>219322</t>
+          <t>254390</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>194461</t>
+          <t>230059</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>242275</t>
+          <t>278039</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>43,79%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>170404</t>
+          <t>172135</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>143685</t>
+          <t>148659</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>197447</t>
+          <t>199168</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>195407</t>
+          <t>203506</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>174942</t>
+          <t>183957</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>214312</t>
+          <t>223089</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>365811</t>
+          <t>375641</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>332070</t>
+          <t>344523</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>402171</t>
+          <t>408543</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>37,93%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>347986</t>
+          <t>358512</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>320943</t>
+          <t>331479</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>374705</t>
+          <t>381988</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>319562</t>
+          <t>342988</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>300657</t>
+          <t>323405</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>340027</t>
+          <t>362537</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,76%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>667548</t>
+          <t>701500</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>631188</t>
+          <t>668598</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>701289</t>
+          <t>732618</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,02%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>128591</t>
+          <t>126420</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>112697</t>
+          <t>110069</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>145188</t>
+          <t>143034</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>157502</t>
+          <t>159441</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>142142</t>
+          <t>142577</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172811</t>
+          <t>175164</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>286093</t>
+          <t>285861</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>259929</t>
+          <t>265133</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>309209</t>
+          <t>310433</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>187459</t>
+          <t>189573</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>170862</t>
+          <t>172959</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>203353</t>
+          <t>205924</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>191626</t>
+          <t>196940</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>176317</t>
+          <t>181217</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>206986</t>
+          <t>213804</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>379085</t>
+          <t>386514</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>355969</t>
+          <t>361942</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>405249</t>
+          <t>407242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,57%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>127957</t>
+          <t>150417</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106942</t>
+          <t>126370</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>147254</t>
+          <t>172590</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>183799</t>
+          <t>206057</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110053</t>
+          <t>184353</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>233090</t>
+          <t>226585</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,0%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>311756</t>
+          <t>356474</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>222189</t>
+          <t>321740</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>361616</t>
+          <t>387112</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>48,69%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>184600</t>
+          <t>222728</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>165303</t>
+          <t>200555</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>205615</t>
+          <t>246775</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>291919</t>
+          <t>215904</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>242628</t>
+          <t>195376</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>365665</t>
+          <t>237608</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>476518</t>
+          <t>438633</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>426658</t>
+          <t>407995</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>566085</t>
+          <t>473367</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>59,54%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18011</t>
+          <t>19135</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12293</t>
+          <t>13480</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>25415</t>
+          <t>27111</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24796</t>
+          <t>26680</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13086</t>
+          <t>20923</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33098</t>
+          <t>33507</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>42806</t>
+          <t>45815</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29880</t>
+          <t>36804</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53504</t>
+          <t>55871</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>160731</t>
+          <t>186530</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>153327</t>
+          <t>178554</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166449</t>
+          <t>192185</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>233983</t>
+          <t>202238</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>225681</t>
+          <t>195411</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>245693</t>
+          <t>207995</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>394715</t>
+          <t>388767</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>384017</t>
+          <t>378711</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407641</t>
+          <t>397778</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>91,53%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>133351</t>
+          <t>133669</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>117824</t>
+          <t>120117</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>148052</t>
+          <t>147937</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,91%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>130596</t>
+          <t>132457</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>119026</t>
+          <t>119734</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>143983</t>
+          <t>146349</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>263947</t>
+          <t>266126</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>246785</t>
+          <t>246350</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>282182</t>
+          <t>286882</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,68%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>136285</t>
+          <t>137038</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>121584</t>
+          <t>122770</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>151812</t>
+          <t>150590</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>126460</t>
+          <t>131293</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>113073</t>
+          <t>117401</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>138030</t>
+          <t>144016</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>262745</t>
+          <t>268331</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>244510</t>
+          <t>247575</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>279907</t>
+          <t>288107</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,91%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>137359</t>
+          <t>152527</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>117006</t>
+          <t>129972</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>164795</t>
+          <t>177661</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>378430</t>
+          <t>211479</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>219390</t>
+          <t>189540</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>616480</t>
+          <t>236445</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>515789</t>
+          <t>364006</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>349389</t>
+          <t>330080</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>854127</t>
+          <t>396055</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>57,96%</t>
+          <t>26,55%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>486920</t>
+          <t>567160</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>459484</t>
+          <t>542026</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>507273</t>
+          <t>589715</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>470835</t>
+          <t>560578</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>232785</t>
+          <t>535612</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>629875</t>
+          <t>582517</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>72,61%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>957755</t>
+          <t>1127738</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>619417</t>
+          <t>1095689</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1124155</t>
+          <t>1161664</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>77,87%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>204313</t>
+          <t>230422</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>87766</t>
+          <t>205488</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>287957</t>
+          <t>257437</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>297225</t>
+          <t>340661</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>274894</t>
+          <t>316226</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>318720</t>
+          <t>364866</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>501538</t>
+          <t>571084</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>302808</t>
+          <t>536779</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>599254</t>
+          <t>610823</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>37,49%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>724407</t>
+          <t>567650</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>640763</t>
+          <t>540635</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>840954</t>
+          <t>592584</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>420506</t>
+          <t>490670</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>399011</t>
+          <t>466465</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>442837</t>
+          <t>515105</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1144914</t>
+          <t>1058319</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1047198</t>
+          <t>1018580</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1343644</t>
+          <t>1092624</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>69,54%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>67,06%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1104702</t>
+          <t>1162000</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>851461</t>
+          <t>1106345</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1212100</t>
+          <t>1221352</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1564793</t>
+          <t>1483525</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1412102</t>
+          <t>1433536</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1968520</t>
+          <t>1533086</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>39,7%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2669494</t>
+          <t>2645524</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2428411</t>
+          <t>2567115</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3056824</t>
+          <t>2736520</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>37,64%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2355115</t>
+          <t>2370762</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2247717</t>
+          <t>2311410</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2608356</t>
+          <t>2426417</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2147487</t>
+          <t>2253429</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1743760</t>
+          <t>2203868</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2300178</t>
+          <t>2303418</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4502603</t>
+          <t>4624192</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4115273</t>
+          <t>4533196</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4743686</t>
+          <t>4702601</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>64,69%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_enfcro_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P2A_enfcro_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con enfermedades crónicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
